--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475972</v>
+        <v>129475991</v>
       </c>
       <c r="B2" t="n">
-        <v>79633</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404620</v>
+        <v>404585</v>
       </c>
       <c r="R2" t="n">
-        <v>6795717</v>
+        <v>6795876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>129476021</v>
       </c>
       <c r="B3" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475973</v>
+        <v>129475972</v>
       </c>
       <c r="B4" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404770</v>
+        <v>404620</v>
       </c>
       <c r="R4" t="n">
-        <v>6795623</v>
+        <v>6795717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>78800</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129475999</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475984</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
         <v>78801</v>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404976</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795654</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129475993</v>
+        <v>129475984</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405005</v>
+        <v>404976</v>
       </c>
       <c r="R9" t="n">
-        <v>6795847</v>
+        <v>6795654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476032</v>
+        <v>129475989</v>
       </c>
       <c r="B10" t="n">
-        <v>92843</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404618</v>
+        <v>404659</v>
       </c>
       <c r="R10" t="n">
-        <v>6795823</v>
+        <v>6796150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475978</v>
+        <v>129476001</v>
       </c>
       <c r="B11" t="n">
-        <v>90575</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404977</v>
+        <v>404789</v>
       </c>
       <c r="R11" t="n">
-        <v>6795858</v>
+        <v>6795606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
         <v>129475994</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R13" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
         <v>129475990</v>
       </c>
       <c r="B14" t="n">
-        <v>81028</v>
+        <v>81029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475989</v>
+        <v>129475978</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>90577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404659</v>
+        <v>404977</v>
       </c>
       <c r="R15" t="n">
-        <v>6796150</v>
+        <v>6795858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475969</v>
+        <v>129476032</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>92845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404983</v>
+        <v>404618</v>
       </c>
       <c r="R16" t="n">
-        <v>6795860</v>
+        <v>6795823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476027</v>
+        <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405008</v>
+        <v>404846</v>
       </c>
       <c r="R17" t="n">
-        <v>6795837</v>
+        <v>6795943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R18" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476028</v>
+        <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404846</v>
+        <v>404597</v>
       </c>
       <c r="R19" t="n">
-        <v>6795943</v>
+        <v>6795875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>129475968</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R21" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>129476008</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129476010</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129475996</v>
       </c>
       <c r="B24" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404614</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129475974</v>
+        <v>129476007</v>
       </c>
       <c r="B25" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405050</v>
+        <v>405036</v>
       </c>
       <c r="R25" t="n">
-        <v>6795647</v>
+        <v>6795690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476000</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404752</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,32 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476000</v>
+        <v>129476024</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404752</v>
+        <v>404978</v>
       </c>
       <c r="R29" t="n">
-        <v>6795618</v>
+        <v>6795580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
         <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B31" t="n">
-        <v>92825</v>
+        <v>78802</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R31" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,7 +3888,7 @@
         <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475986</v>
+        <v>129476030</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404709</v>
+        <v>404647</v>
       </c>
       <c r="R34" t="n">
-        <v>6795944</v>
+        <v>6796135</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>129475995</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4423,7 @@
         <v>129476018</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476022</v>
+        <v>129475961</v>
       </c>
       <c r="B38" t="n">
-        <v>78709</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404666</v>
+        <v>405083</v>
       </c>
       <c r="R38" t="n">
-        <v>6796033</v>
+        <v>6795691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476002</v>
+        <v>129476022</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404928</v>
+        <v>404666</v>
       </c>
       <c r="R39" t="n">
-        <v>6795555</v>
+        <v>6796033</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>92845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R40" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,7 +4851,7 @@
         <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476031</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>92843</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404617</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795929</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R44" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
         <v>129476005</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B48" t="n">
-        <v>92825</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
         <v>129475971</v>
       </c>
       <c r="B49" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
         <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129475976</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>405003</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795853</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R56" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R57" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>78802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R58" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
         <v>129475977</v>
       </c>
       <c r="B59" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476009</v>
+        <v>129476020</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>78710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404999</v>
+        <v>405094</v>
       </c>
       <c r="R60" t="n">
-        <v>6795773</v>
+        <v>6795659</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
         <v>129476017</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476020</v>
+        <v>129476009</v>
       </c>
       <c r="B62" t="n">
-        <v>78709</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,21 +7106,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>405094</v>
+        <v>404999</v>
       </c>
       <c r="R62" t="n">
-        <v>6795659</v>
+        <v>6795773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7205,7 +7205,7 @@
         <v>129476006</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475991</v>
+        <v>129476021</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404585</v>
+        <v>405019</v>
       </c>
       <c r="R2" t="n">
-        <v>6795876</v>
+        <v>6795811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B3" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R3" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475972</v>
+        <v>129475973</v>
       </c>
       <c r="B4" t="n">
         <v>79634</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404620</v>
+        <v>404770</v>
       </c>
       <c r="R4" t="n">
-        <v>6795717</v>
+        <v>6795623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475973</v>
+        <v>129475991</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404770</v>
+        <v>404585</v>
       </c>
       <c r="R5" t="n">
-        <v>6795623</v>
+        <v>6795876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1213,7 +1213,7 @@
         <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475989</v>
+        <v>129476001</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404659</v>
+        <v>404789</v>
       </c>
       <c r="R10" t="n">
-        <v>6796150</v>
+        <v>6795606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476001</v>
+        <v>129475994</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404789</v>
+        <v>404596</v>
       </c>
       <c r="R11" t="n">
-        <v>6795606</v>
+        <v>6796024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475994</v>
+        <v>129476032</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>92849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404596</v>
+        <v>404618</v>
       </c>
       <c r="R12" t="n">
-        <v>6796024</v>
+        <v>6795823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>90581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R13" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475990</v>
+        <v>129475969</v>
       </c>
       <c r="B14" t="n">
-        <v>81029</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404665</v>
+        <v>404983</v>
       </c>
       <c r="R14" t="n">
-        <v>6796141</v>
+        <v>6795860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475978</v>
+        <v>129475990</v>
       </c>
       <c r="B15" t="n">
-        <v>90577</v>
+        <v>81029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404977</v>
+        <v>404665</v>
       </c>
       <c r="R15" t="n">
-        <v>6795858</v>
+        <v>6796141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476032</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>92845</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404618</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6795823</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129475975</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405119</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795655</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R24" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B28" t="n">
-        <v>79634</v>
+        <v>92831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R28" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476024</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>92827</v>
+        <v>79634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404978</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795580</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475986</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404709</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6795944</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129475986</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404709</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6795944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4102,7 @@
         <v>129476030</v>
       </c>
       <c r="B34" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476031</v>
+        <v>129476019</v>
       </c>
       <c r="B40" t="n">
-        <v>92845</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404617</v>
+        <v>404638</v>
       </c>
       <c r="R40" t="n">
-        <v>6795929</v>
+        <v>6796042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476031</v>
       </c>
       <c r="B41" t="n">
-        <v>79663</v>
+        <v>92849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404617</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6795929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129475982</v>
+        <v>129476005</v>
       </c>
       <c r="B44" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404585</v>
+        <v>404990</v>
       </c>
       <c r="R44" t="n">
-        <v>6795876</v>
+        <v>6795675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,7 +5493,7 @@
         <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475988</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404648</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6796068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
         <v>79663</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475970</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404726</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B55" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R55" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475972</v>
+        <v>129475991</v>
       </c>
       <c r="B3" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404620</v>
+        <v>404585</v>
       </c>
       <c r="R3" t="n">
-        <v>6795717</v>
+        <v>6795876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475973</v>
+        <v>129475972</v>
       </c>
       <c r="B4" t="n">
         <v>79634</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404770</v>
+        <v>404620</v>
       </c>
       <c r="R4" t="n">
-        <v>6795623</v>
+        <v>6795717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1213,7 +1213,7 @@
         <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R10" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475994</v>
+        <v>129475989</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404596</v>
+        <v>404659</v>
       </c>
       <c r="R11" t="n">
-        <v>6796024</v>
+        <v>6796150</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476032</v>
+        <v>129475990</v>
       </c>
       <c r="B12" t="n">
-        <v>92849</v>
+        <v>81029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404618</v>
+        <v>404665</v>
       </c>
       <c r="R12" t="n">
-        <v>6795823</v>
+        <v>6796141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475969</v>
+        <v>129476001</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404983</v>
+        <v>404789</v>
       </c>
       <c r="R14" t="n">
-        <v>6795860</v>
+        <v>6795606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475990</v>
+        <v>129475994</v>
       </c>
       <c r="B15" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404665</v>
+        <v>404596</v>
       </c>
       <c r="R15" t="n">
-        <v>6796141</v>
+        <v>6796024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129476032</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>92850</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404618</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6795823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476007</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405036</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795690</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129476030</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>92832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>404647</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6796135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475986</v>
+        <v>129475963</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404709</v>
+        <v>404602</v>
       </c>
       <c r="R33" t="n">
-        <v>6795944</v>
+        <v>6796090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>92831</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R34" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4851,7 +4851,7 @@
         <v>129476031</v>
       </c>
       <c r="B41" t="n">
-        <v>92849</v>
+        <v>92850</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475988</v>
+        <v>129475964</v>
       </c>
       <c r="B50" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404648</v>
+        <v>405045</v>
       </c>
       <c r="R50" t="n">
-        <v>6796068</v>
+        <v>6795657</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475970</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>404726</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795995</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475970</v>
+        <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404726</v>
+        <v>404648</v>
       </c>
       <c r="R53" t="n">
-        <v>6795995</v>
+        <v>6796068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B2" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R2" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R3" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475972</v>
+        <v>129476021</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>78710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404620</v>
+        <v>405019</v>
       </c>
       <c r="R4" t="n">
-        <v>6795717</v>
+        <v>6795811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475973</v>
+        <v>129475991</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404770</v>
+        <v>404585</v>
       </c>
       <c r="R5" t="n">
-        <v>6795623</v>
+        <v>6795876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475969</v>
+        <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>81029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404983</v>
+        <v>404665</v>
       </c>
       <c r="R10" t="n">
-        <v>6795860</v>
+        <v>6796141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475989</v>
+        <v>129475978</v>
       </c>
       <c r="B11" t="n">
-        <v>78802</v>
+        <v>90582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404659</v>
+        <v>404977</v>
       </c>
       <c r="R11" t="n">
-        <v>6796150</v>
+        <v>6795858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475990</v>
+        <v>129476001</v>
       </c>
       <c r="B12" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404665</v>
+        <v>404789</v>
       </c>
       <c r="R12" t="n">
-        <v>6796141</v>
+        <v>6795606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475978</v>
+        <v>129475994</v>
       </c>
       <c r="B13" t="n">
-        <v>90582</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404977</v>
+        <v>404596</v>
       </c>
       <c r="R13" t="n">
-        <v>6795858</v>
+        <v>6796024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R14" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475994</v>
+        <v>129476032</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>92850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404596</v>
+        <v>404618</v>
       </c>
       <c r="R15" t="n">
-        <v>6796024</v>
+        <v>6795823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476032</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>92850</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404618</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6795823</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B25" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476000</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404752</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129476024</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>404978</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475992</v>
+        <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>78801</v>
+        <v>92832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404759</v>
+        <v>404647</v>
       </c>
       <c r="R30" t="n">
-        <v>6795618</v>
+        <v>6796135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B31" t="n">
-        <v>92832</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R31" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,7 +3992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B33" t="n">
         <v>79663</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R33" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R39" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>92850</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R40" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>92850</v>
+        <v>79663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R41" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B49" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,7 +5918,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
         <v>79663</v>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476014</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404889</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795906</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R55" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476015</v>
+        <v>129475976</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404835</v>
+        <v>405003</v>
       </c>
       <c r="R56" t="n">
-        <v>6795953</v>
+        <v>6795853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476007</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405036</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795690</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>92832</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>92832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129475961</v>
       </c>
       <c r="B37" t="n">
-        <v>78710</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>405083</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795691</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129476022</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>404666</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6796033</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B47" t="n">
-        <v>92832</v>
+        <v>78802</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R47" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>92832</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R48" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1641,7 +1641,7 @@
         <v>129475978</v>
       </c>
       <c r="B11" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476001</v>
+        <v>129475994</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404789</v>
+        <v>404596</v>
       </c>
       <c r="R12" t="n">
-        <v>6795606</v>
+        <v>6796024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475994</v>
+        <v>129475969</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404596</v>
+        <v>404983</v>
       </c>
       <c r="R13" t="n">
-        <v>6796024</v>
+        <v>6795860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475969</v>
+        <v>129476032</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>92853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404983</v>
+        <v>404618</v>
       </c>
       <c r="R14" t="n">
-        <v>6795860</v>
+        <v>6795823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476032</v>
+        <v>129476001</v>
       </c>
       <c r="B15" t="n">
-        <v>92850</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404618</v>
+        <v>404789</v>
       </c>
       <c r="R15" t="n">
-        <v>6795823</v>
+        <v>6795606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476008</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>405029</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795732</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129476000</v>
       </c>
       <c r="B25" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>404752</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795618</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476024</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404978</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129476007</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>405036</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795690</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,7 +3995,7 @@
         <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129475961</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>78710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>405083</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795691</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476022</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404666</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6796033</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476031</v>
+        <v>129476019</v>
       </c>
       <c r="B40" t="n">
-        <v>92850</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404617</v>
+        <v>404638</v>
       </c>
       <c r="R40" t="n">
-        <v>6795929</v>
+        <v>6796042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>92853</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R44" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476005</v>
       </c>
       <c r="B46" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404990</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,7 +5600,7 @@
         <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476009</v>
+        <v>129476006</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404999</v>
+        <v>405010</v>
       </c>
       <c r="R62" t="n">
-        <v>6795773</v>
+        <v>6795690</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,7 +7202,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476006</v>
+        <v>129476009</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405010</v>
+        <v>404999</v>
       </c>
       <c r="R63" t="n">
-        <v>6795690</v>
+        <v>6795773</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R7" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475978</v>
+        <v>129476001</v>
       </c>
       <c r="B11" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404977</v>
+        <v>404789</v>
       </c>
       <c r="R11" t="n">
-        <v>6795858</v>
+        <v>6795606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R13" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R15" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476010</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404943</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795899</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476008</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405029</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795732</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476000</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404752</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795618</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476007</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405036</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795690</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>404647</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6796135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475963</v>
       </c>
       <c r="B32" t="n">
         <v>79663</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404602</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6796090</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475986</v>
+        <v>129475992</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404709</v>
+        <v>404759</v>
       </c>
       <c r="R34" t="n">
-        <v>6795944</v>
+        <v>6795618</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B37" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R39" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>92853</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R40" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B42" t="n">
-        <v>92853</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R42" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,7 +5169,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476016</v>
+        <v>129476005</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404829</v>
+        <v>404990</v>
       </c>
       <c r="R44" t="n">
-        <v>6795954</v>
+        <v>6795675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476005</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404990</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795675</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475971</v>
+        <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404652</v>
+        <v>404643</v>
       </c>
       <c r="R47" t="n">
-        <v>6796177</v>
+        <v>6796056</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R57" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B58" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R58" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7095,7 +7095,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476006</v>
+        <v>129476009</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>405010</v>
+        <v>404999</v>
       </c>
       <c r="R62" t="n">
-        <v>6795690</v>
+        <v>6795773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,7 +7202,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476009</v>
+        <v>129476006</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404999</v>
+        <v>405010</v>
       </c>
       <c r="R63" t="n">
-        <v>6795773</v>
+        <v>6795690</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475972</v>
+        <v>129476021</v>
       </c>
       <c r="B2" t="n">
-        <v>79634</v>
+        <v>78710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404620</v>
+        <v>405019</v>
       </c>
       <c r="R2" t="n">
-        <v>6795717</v>
+        <v>6795811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475973</v>
+        <v>129475991</v>
       </c>
       <c r="B3" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404770</v>
+        <v>404585</v>
       </c>
       <c r="R3" t="n">
-        <v>6795623</v>
+        <v>6795876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B4" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R4" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B7" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476001</v>
+        <v>129475978</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>90585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404789</v>
+        <v>404977</v>
       </c>
       <c r="R11" t="n">
-        <v>6795606</v>
+        <v>6795858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475994</v>
+        <v>129476032</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>92853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404596</v>
+        <v>404618</v>
       </c>
       <c r="R12" t="n">
-        <v>6796024</v>
+        <v>6795823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475978</v>
+        <v>129476001</v>
       </c>
       <c r="B13" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404977</v>
+        <v>404789</v>
       </c>
       <c r="R13" t="n">
-        <v>6795858</v>
+        <v>6795606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476032</v>
+        <v>129475994</v>
       </c>
       <c r="B14" t="n">
-        <v>92853</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404618</v>
+        <v>404596</v>
       </c>
       <c r="R14" t="n">
-        <v>6795823</v>
+        <v>6796024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476028</v>
+        <v>129475981</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404846</v>
+        <v>404597</v>
       </c>
       <c r="R17" t="n">
-        <v>6795943</v>
+        <v>6795875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476027</v>
+        <v>129476028</v>
       </c>
       <c r="B18" t="n">
         <v>92835</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405008</v>
+        <v>404846</v>
       </c>
       <c r="R18" t="n">
-        <v>6795837</v>
+        <v>6795943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R19" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129475975</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>405119</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129476008</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>405029</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129475996</v>
       </c>
       <c r="B24" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404614</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
         <v>79663</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475986</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404709</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795944</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475992</v>
+        <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404759</v>
+        <v>404709</v>
       </c>
       <c r="R34" t="n">
-        <v>6795618</v>
+        <v>6795944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R39" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476005</v>
+        <v>129475982</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404990</v>
+        <v>404585</v>
       </c>
       <c r="R44" t="n">
-        <v>6795675</v>
+        <v>6795876</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129476005</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404990</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B47" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R47" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404643</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6796056</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B49" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R55" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R57" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R58" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476020</v>
+        <v>129476017</v>
       </c>
       <c r="B60" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>405094</v>
+        <v>404825</v>
       </c>
       <c r="R60" t="n">
-        <v>6795659</v>
+        <v>6795955</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,7 +6988,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476017</v>
+        <v>129476009</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404825</v>
+        <v>404999</v>
       </c>
       <c r="R61" t="n">
-        <v>6795955</v>
+        <v>6795773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,7 +7095,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476009</v>
+        <v>129476006</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404999</v>
+        <v>405010</v>
       </c>
       <c r="R62" t="n">
-        <v>6795773</v>
+        <v>6795690</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476006</v>
+        <v>129476020</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405010</v>
+        <v>405094</v>
       </c>
       <c r="R63" t="n">
-        <v>6795690</v>
+        <v>6795659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129476021</v>
+        <v>129475991</v>
       </c>
       <c r="B2" t="n">
-        <v>78710</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405019</v>
+        <v>404585</v>
       </c>
       <c r="R2" t="n">
-        <v>6795811</v>
+        <v>6795876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475991</v>
+        <v>129476021</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404585</v>
+        <v>405019</v>
       </c>
       <c r="R3" t="n">
-        <v>6795876</v>
+        <v>6795811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R7" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475990</v>
+        <v>129476001</v>
       </c>
       <c r="B10" t="n">
-        <v>81029</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404665</v>
+        <v>404789</v>
       </c>
       <c r="R10" t="n">
-        <v>6796141</v>
+        <v>6795606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475978</v>
+        <v>129475994</v>
       </c>
       <c r="B11" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404977</v>
+        <v>404596</v>
       </c>
       <c r="R11" t="n">
-        <v>6795858</v>
+        <v>6796024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476032</v>
+        <v>129475989</v>
       </c>
       <c r="B12" t="n">
-        <v>92853</v>
+        <v>78802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404618</v>
+        <v>404659</v>
       </c>
       <c r="R12" t="n">
-        <v>6795823</v>
+        <v>6796150</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476001</v>
+        <v>129476032</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>92853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404789</v>
+        <v>404618</v>
       </c>
       <c r="R13" t="n">
-        <v>6795606</v>
+        <v>6795823</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475994</v>
+        <v>129475969</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404596</v>
+        <v>404983</v>
       </c>
       <c r="R14" t="n">
-        <v>6796024</v>
+        <v>6795860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R15" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129475990</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>81029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404665</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6796141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129475981</v>
+        <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404597</v>
+        <v>404846</v>
       </c>
       <c r="R17" t="n">
-        <v>6795875</v>
+        <v>6795943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476028</v>
+        <v>129476027</v>
       </c>
       <c r="B18" t="n">
         <v>92835</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404846</v>
+        <v>405008</v>
       </c>
       <c r="R18" t="n">
-        <v>6795943</v>
+        <v>6795837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476027</v>
+        <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405008</v>
+        <v>404597</v>
       </c>
       <c r="R19" t="n">
-        <v>6795837</v>
+        <v>6795875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129475975</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405119</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795655</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R24" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129475974</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>79634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>405050</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476024</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404978</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129475997</v>
       </c>
       <c r="B29" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404617</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475986</v>
+        <v>129476030</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404709</v>
+        <v>404647</v>
       </c>
       <c r="R34" t="n">
-        <v>6795944</v>
+        <v>6796135</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B37" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R39" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129475982</v>
+        <v>129476005</v>
       </c>
       <c r="B44" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404585</v>
+        <v>404990</v>
       </c>
       <c r="R44" t="n">
-        <v>6795876</v>
+        <v>6795675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475991</v>
+        <v>129475972</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404585</v>
+        <v>404620</v>
       </c>
       <c r="R2" t="n">
-        <v>6795876</v>
+        <v>6795717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129476021</v>
+        <v>129475973</v>
       </c>
       <c r="B3" t="n">
-        <v>78710</v>
+        <v>79634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405019</v>
+        <v>404770</v>
       </c>
       <c r="R3" t="n">
-        <v>6795811</v>
+        <v>6795623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475972</v>
+        <v>129475991</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404620</v>
+        <v>404585</v>
       </c>
       <c r="R4" t="n">
-        <v>6795717</v>
+        <v>6795876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475973</v>
+        <v>129476021</v>
       </c>
       <c r="B5" t="n">
-        <v>79634</v>
+        <v>78710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404770</v>
+        <v>405019</v>
       </c>
       <c r="R5" t="n">
-        <v>6795623</v>
+        <v>6795811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476001</v>
+        <v>129475989</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404789</v>
+        <v>404659</v>
       </c>
       <c r="R10" t="n">
-        <v>6795606</v>
+        <v>6796150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475994</v>
+        <v>129475969</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404596</v>
+        <v>404983</v>
       </c>
       <c r="R11" t="n">
-        <v>6796024</v>
+        <v>6795860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475989</v>
+        <v>129475978</v>
       </c>
       <c r="B12" t="n">
-        <v>78802</v>
+        <v>90585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404659</v>
+        <v>404977</v>
       </c>
       <c r="R12" t="n">
-        <v>6796150</v>
+        <v>6795858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476032</v>
+        <v>129475990</v>
       </c>
       <c r="B13" t="n">
-        <v>92853</v>
+        <v>81029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404618</v>
+        <v>404665</v>
       </c>
       <c r="R13" t="n">
-        <v>6795823</v>
+        <v>6796141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475969</v>
+        <v>129476001</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404983</v>
+        <v>404789</v>
       </c>
       <c r="R14" t="n">
-        <v>6795860</v>
+        <v>6795606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475978</v>
+        <v>129475994</v>
       </c>
       <c r="B15" t="n">
-        <v>90585</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404977</v>
+        <v>404596</v>
       </c>
       <c r="R15" t="n">
-        <v>6795858</v>
+        <v>6796024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475990</v>
+        <v>129476032</v>
       </c>
       <c r="B16" t="n">
-        <v>81029</v>
+        <v>92853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404665</v>
+        <v>404618</v>
       </c>
       <c r="R16" t="n">
-        <v>6796141</v>
+        <v>6795823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79634</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R26" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475992</v>
+        <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>78801</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404759</v>
+        <v>404647</v>
       </c>
       <c r="R30" t="n">
-        <v>6795618</v>
+        <v>6796135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475986</v>
+        <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404709</v>
+        <v>405049</v>
       </c>
       <c r="R33" t="n">
-        <v>6795944</v>
+        <v>6795727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R34" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R39" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,7 +5169,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R44" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129476005</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404990</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129475976</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>405003</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795853</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B56" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R56" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R57" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B58" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R58" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475972</v>
+        <v>129475991</v>
       </c>
       <c r="B2" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404620</v>
+        <v>404585</v>
       </c>
       <c r="R2" t="n">
-        <v>6795717</v>
+        <v>6795876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475973</v>
+        <v>129475972</v>
       </c>
       <c r="B3" t="n">
         <v>79634</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404770</v>
+        <v>404620</v>
       </c>
       <c r="R3" t="n">
-        <v>6795623</v>
+        <v>6795717</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R4" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B7" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475989</v>
+        <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>81029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404659</v>
+        <v>404665</v>
       </c>
       <c r="R10" t="n">
-        <v>6796150</v>
+        <v>6796141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>90585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R11" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475978</v>
+        <v>129476032</v>
       </c>
       <c r="B12" t="n">
-        <v>90585</v>
+        <v>92853</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404977</v>
+        <v>404618</v>
       </c>
       <c r="R12" t="n">
-        <v>6795858</v>
+        <v>6795823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475990</v>
+        <v>129475989</v>
       </c>
       <c r="B13" t="n">
-        <v>81029</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404665</v>
+        <v>404659</v>
       </c>
       <c r="R13" t="n">
-        <v>6796141</v>
+        <v>6796150</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476032</v>
+        <v>129475969</v>
       </c>
       <c r="B16" t="n">
-        <v>92853</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404618</v>
+        <v>404983</v>
       </c>
       <c r="R16" t="n">
-        <v>6795823</v>
+        <v>6795860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R26" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476007</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405036</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795690</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476000</v>
+        <v>129476024</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404752</v>
+        <v>404978</v>
       </c>
       <c r="R28" t="n">
-        <v>6795618</v>
+        <v>6795580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B37" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R39" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5169,7 +5169,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476016</v>
+        <v>129476005</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404829</v>
+        <v>404990</v>
       </c>
       <c r="R44" t="n">
-        <v>6795954</v>
+        <v>6795675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R47" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B49" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475988</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404648</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6796068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
         <v>79663</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475970</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404726</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129475976</v>
+        <v>129476015</v>
       </c>
       <c r="B55" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>405003</v>
+        <v>404835</v>
       </c>
       <c r="R55" t="n">
-        <v>6795853</v>
+        <v>6795953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R56" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R57" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R58" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,7 +6881,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476017</v>
+        <v>129476009</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404825</v>
+        <v>404999</v>
       </c>
       <c r="R60" t="n">
-        <v>6795955</v>
+        <v>6795773</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,7 +6988,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476009</v>
+        <v>129476006</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404999</v>
+        <v>405010</v>
       </c>
       <c r="R61" t="n">
-        <v>6795773</v>
+        <v>6795690</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476006</v>
+        <v>129476020</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,21 +7106,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>405010</v>
+        <v>405094</v>
       </c>
       <c r="R62" t="n">
-        <v>6795690</v>
+        <v>6795659</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476020</v>
+        <v>129476017</v>
       </c>
       <c r="B63" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405094</v>
+        <v>404825</v>
       </c>
       <c r="R63" t="n">
-        <v>6795659</v>
+        <v>6795955</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475991</v>
+        <v>129475972</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404585</v>
+        <v>404620</v>
       </c>
       <c r="R2" t="n">
-        <v>6795876</v>
+        <v>6795717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475972</v>
+        <v>129475973</v>
       </c>
       <c r="B3" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404620</v>
+        <v>404770</v>
       </c>
       <c r="R3" t="n">
-        <v>6795717</v>
+        <v>6795623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475973</v>
+        <v>129476021</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404770</v>
+        <v>405019</v>
       </c>
       <c r="R4" t="n">
-        <v>6795623</v>
+        <v>6795811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129476021</v>
+        <v>129475991</v>
       </c>
       <c r="B5" t="n">
-        <v>78710</v>
+        <v>78827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405019</v>
+        <v>404585</v>
       </c>
       <c r="R5" t="n">
-        <v>6795811</v>
+        <v>6795876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129475999</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475993</v>
+        <v>129475984</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>78828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405005</v>
+        <v>404976</v>
       </c>
       <c r="R7" t="n">
-        <v>6795847</v>
+        <v>6795654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>92829</v>
+        <v>78827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129475984</v>
+        <v>129476033</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>92857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404976</v>
+        <v>404617</v>
       </c>
       <c r="R9" t="n">
-        <v>6795654</v>
+        <v>6795935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475990</v>
+        <v>129475989</v>
       </c>
       <c r="B10" t="n">
-        <v>81029</v>
+        <v>78828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404665</v>
+        <v>404659</v>
       </c>
       <c r="R10" t="n">
-        <v>6796141</v>
+        <v>6796150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475978</v>
+        <v>129475990</v>
       </c>
       <c r="B11" t="n">
-        <v>90585</v>
+        <v>81055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404977</v>
+        <v>404665</v>
       </c>
       <c r="R11" t="n">
-        <v>6795858</v>
+        <v>6796141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476032</v>
+        <v>129476001</v>
       </c>
       <c r="B12" t="n">
-        <v>92853</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404618</v>
+        <v>404789</v>
       </c>
       <c r="R12" t="n">
-        <v>6795823</v>
+        <v>6795606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475989</v>
+        <v>129475994</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404659</v>
+        <v>404596</v>
       </c>
       <c r="R13" t="n">
-        <v>6796150</v>
+        <v>6796024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R14" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475994</v>
+        <v>129475978</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>90613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404596</v>
+        <v>404977</v>
       </c>
       <c r="R15" t="n">
-        <v>6796024</v>
+        <v>6795858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475969</v>
+        <v>129476032</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>92881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404983</v>
+        <v>404618</v>
       </c>
       <c r="R16" t="n">
-        <v>6795860</v>
+        <v>6795823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129475968</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129476010</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129475996</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476007</v>
+        <v>129475974</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405036</v>
+        <v>405050</v>
       </c>
       <c r="R25" t="n">
-        <v>6795690</v>
+        <v>6795647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B29" t="n">
-        <v>79634</v>
+        <v>92863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129475986</v>
       </c>
       <c r="B30" t="n">
-        <v>79663</v>
+        <v>78828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>404709</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6795944</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>79689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>78827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>79689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>405049</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475986</v>
+        <v>129476030</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>92863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404709</v>
+        <v>404647</v>
       </c>
       <c r="R34" t="n">
-        <v>6795944</v>
+        <v>6796135</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
         <v>129475995</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R39" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B40" t="n">
-        <v>92853</v>
+        <v>79689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R40" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>92881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129476005</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B47" t="n">
-        <v>79663</v>
+        <v>78828</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R47" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>79689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
         <v>129476029</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475988</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404648</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6796068</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475970</v>
+        <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>79663</v>
+        <v>78828</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404726</v>
+        <v>404648</v>
       </c>
       <c r="R53" t="n">
-        <v>6795995</v>
+        <v>6796068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
         <v>129476004</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>129476015</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>129475976</v>
       </c>
       <c r="B56" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>129475977</v>
       </c>
       <c r="B59" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476009</v>
+        <v>129476020</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404999</v>
+        <v>405094</v>
       </c>
       <c r="R60" t="n">
-        <v>6795773</v>
+        <v>6795659</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476006</v>
+        <v>129476017</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>405010</v>
+        <v>404825</v>
       </c>
       <c r="R61" t="n">
-        <v>6795690</v>
+        <v>6795955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476020</v>
+        <v>129476009</v>
       </c>
       <c r="B62" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,21 +7106,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>405094</v>
+        <v>404999</v>
       </c>
       <c r="R62" t="n">
-        <v>6795659</v>
+        <v>6795773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476017</v>
+        <v>129476006</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404825</v>
+        <v>405010</v>
       </c>
       <c r="R63" t="n">
-        <v>6795955</v>
+        <v>6795690</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129476021</v>
+        <v>129475991</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405019</v>
+        <v>404585</v>
       </c>
       <c r="R4" t="n">
-        <v>6795811</v>
+        <v>6795876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129476021</v>
       </c>
       <c r="B5" t="n">
-        <v>78827</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>405019</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475989</v>
+        <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>78828</v>
+        <v>81055</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404659</v>
+        <v>404665</v>
       </c>
       <c r="R10" t="n">
-        <v>6796150</v>
+        <v>6796141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475990</v>
+        <v>129476001</v>
       </c>
       <c r="B11" t="n">
-        <v>81055</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404665</v>
+        <v>404789</v>
       </c>
       <c r="R11" t="n">
-        <v>6796141</v>
+        <v>6795606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476001</v>
+        <v>129475994</v>
       </c>
       <c r="B12" t="n">
         <v>79070</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404789</v>
+        <v>404596</v>
       </c>
       <c r="R12" t="n">
-        <v>6795606</v>
+        <v>6796024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475994</v>
+        <v>129475969</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404596</v>
+        <v>404983</v>
       </c>
       <c r="R13" t="n">
-        <v>6796024</v>
+        <v>6795860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>90613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R14" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475978</v>
+        <v>129476032</v>
       </c>
       <c r="B15" t="n">
-        <v>90613</v>
+        <v>92881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404977</v>
+        <v>404618</v>
       </c>
       <c r="R15" t="n">
-        <v>6795858</v>
+        <v>6795823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476032</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>92881</v>
+        <v>78828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404618</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6795823</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475986</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>78828</v>
+        <v>79689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404709</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6795944</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>78827</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
-        <v>78827</v>
+        <v>79689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>92863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>92863</v>
+        <v>78828</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R34" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
-        <v>78828</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>78828</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B55" t="n">
         <v>79070</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129475976</v>
+        <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79660</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>405003</v>
+        <v>404835</v>
       </c>
       <c r="R56" t="n">
-        <v>6795853</v>
+        <v>6795953</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129475972</v>
       </c>
       <c r="B2" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129475973</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475991</v>
+        <v>129476021</v>
       </c>
       <c r="B4" t="n">
-        <v>78827</v>
+        <v>78741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404585</v>
+        <v>405019</v>
       </c>
       <c r="R4" t="n">
-        <v>6795876</v>
+        <v>6795811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129476021</v>
+        <v>129475991</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405019</v>
+        <v>404585</v>
       </c>
       <c r="R5" t="n">
-        <v>6795811</v>
+        <v>6795876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129475999</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475984</v>
+        <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>78828</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404976</v>
+        <v>404617</v>
       </c>
       <c r="R7" t="n">
-        <v>6795654</v>
+        <v>6795935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129476033</v>
+        <v>129475984</v>
       </c>
       <c r="B9" t="n">
-        <v>92857</v>
+        <v>78833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404617</v>
+        <v>404976</v>
       </c>
       <c r="R9" t="n">
-        <v>6795935</v>
+        <v>6795654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>81055</v>
+        <v>81060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476001</v>
+        <v>129475969</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404789</v>
+        <v>404983</v>
       </c>
       <c r="R11" t="n">
-        <v>6795606</v>
+        <v>6795860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475994</v>
+        <v>129475989</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404596</v>
+        <v>404659</v>
       </c>
       <c r="R12" t="n">
-        <v>6796024</v>
+        <v>6796150</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>79689</v>
+        <v>90619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R13" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475978</v>
+        <v>129476032</v>
       </c>
       <c r="B14" t="n">
-        <v>90613</v>
+        <v>92887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404977</v>
+        <v>404618</v>
       </c>
       <c r="R14" t="n">
-        <v>6795858</v>
+        <v>6795823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476032</v>
+        <v>129476001</v>
       </c>
       <c r="B15" t="n">
-        <v>92881</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404618</v>
+        <v>404789</v>
       </c>
       <c r="R15" t="n">
-        <v>6795823</v>
+        <v>6795606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129475994</v>
       </c>
       <c r="B16" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404596</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6796024</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129475968</v>
       </c>
       <c r="B20" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129476010</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129475996</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129475974</v>
       </c>
       <c r="B25" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476024</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404978</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476024</v>
+        <v>129475997</v>
       </c>
       <c r="B29" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404978</v>
+        <v>404617</v>
       </c>
       <c r="R29" t="n">
-        <v>6795580</v>
+        <v>6795687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>79689</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>404647</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6796135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B31" t="n">
-        <v>78827</v>
+        <v>79694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>78832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>79694</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>405049</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4102,7 @@
         <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129475995</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129475965</v>
       </c>
       <c r="B40" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>92887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476031</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>92881</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404617</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795929</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476005</v>
+        <v>129475982</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404990</v>
+        <v>404585</v>
       </c>
       <c r="R44" t="n">
-        <v>6795675</v>
+        <v>6795876</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129476005</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404990</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>78828</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,7 +5600,7 @@
         <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>92863</v>
+        <v>78833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475988</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404648</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6796068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475970</v>
       </c>
       <c r="B53" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404726</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
         <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>129476004</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B57" t="n">
-        <v>92863</v>
+        <v>78833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R57" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B58" t="n">
-        <v>78828</v>
+        <v>92869</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R58" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
         <v>129475977</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>129476020</v>
       </c>
       <c r="B60" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>129476017</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129476009</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>129476006</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475972</v>
+        <v>129476021</v>
       </c>
       <c r="B2" t="n">
-        <v>79665</v>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404620</v>
+        <v>405019</v>
       </c>
       <c r="R2" t="n">
-        <v>6795717</v>
+        <v>6795811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475973</v>
+        <v>129475991</v>
       </c>
       <c r="B3" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404770</v>
+        <v>404585</v>
       </c>
       <c r="R3" t="n">
-        <v>6795623</v>
+        <v>6795876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B4" t="n">
-        <v>78741</v>
+        <v>79666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R4" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>79666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129475999</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129475984</v>
       </c>
       <c r="B9" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475990</v>
+        <v>129476032</v>
       </c>
       <c r="B10" t="n">
-        <v>81060</v>
+        <v>92888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404665</v>
+        <v>404618</v>
       </c>
       <c r="R10" t="n">
-        <v>6796141</v>
+        <v>6795823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475969</v>
+        <v>129475990</v>
       </c>
       <c r="B11" t="n">
-        <v>79694</v>
+        <v>81061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404983</v>
+        <v>404665</v>
       </c>
       <c r="R11" t="n">
-        <v>6795860</v>
+        <v>6796141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475989</v>
+        <v>129475969</v>
       </c>
       <c r="B12" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404659</v>
+        <v>404983</v>
       </c>
       <c r="R12" t="n">
-        <v>6796150</v>
+        <v>6795860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475978</v>
+        <v>129476001</v>
       </c>
       <c r="B13" t="n">
-        <v>90619</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404977</v>
+        <v>404789</v>
       </c>
       <c r="R13" t="n">
-        <v>6795858</v>
+        <v>6795606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476032</v>
+        <v>129475994</v>
       </c>
       <c r="B14" t="n">
-        <v>92887</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404618</v>
+        <v>404596</v>
       </c>
       <c r="R14" t="n">
-        <v>6795823</v>
+        <v>6796024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476001</v>
+        <v>129475978</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>90620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404789</v>
+        <v>404977</v>
       </c>
       <c r="R15" t="n">
-        <v>6795606</v>
+        <v>6795858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475994</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404596</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6796024</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476028</v>
+        <v>129475981</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>78834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404846</v>
+        <v>404597</v>
       </c>
       <c r="R17" t="n">
-        <v>6795943</v>
+        <v>6795875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476027</v>
+        <v>129476028</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405008</v>
+        <v>404846</v>
       </c>
       <c r="R18" t="n">
-        <v>6795837</v>
+        <v>6795943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>92870</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R19" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>129475968</v>
       </c>
       <c r="B20" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129475975</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>405119</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129476008</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>405029</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129475996</v>
       </c>
       <c r="B24" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404614</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79665</v>
+        <v>92870</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476007</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405036</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795690</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476000</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404752</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795618</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
         <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475963</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404602</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6796090</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B32" t="n">
-        <v>78832</v>
+        <v>79695</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,7 +3995,7 @@
         <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129475995</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129475965</v>
       </c>
       <c r="B40" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>129476031</v>
       </c>
       <c r="B41" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>129475982</v>
       </c>
       <c r="B44" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>129476005</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>129476029</v>
       </c>
       <c r="B47" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475988</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404648</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6796068</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475970</v>
+        <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404726</v>
+        <v>404648</v>
       </c>
       <c r="R53" t="n">
-        <v>6795995</v>
+        <v>6796068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
         <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>129476004</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>129475985</v>
       </c>
       <c r="B57" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>129476026</v>
       </c>
       <c r="B58" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>129475977</v>
       </c>
       <c r="B59" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>129476020</v>
       </c>
       <c r="B60" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>129476017</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>129476009</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>129476006</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476032</v>
+        <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>92888</v>
+        <v>81061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404618</v>
+        <v>404665</v>
       </c>
       <c r="R10" t="n">
-        <v>6795823</v>
+        <v>6796141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475990</v>
+        <v>129476001</v>
       </c>
       <c r="B11" t="n">
-        <v>81061</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404665</v>
+        <v>404789</v>
       </c>
       <c r="R11" t="n">
-        <v>6796141</v>
+        <v>6795606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475969</v>
+        <v>129475994</v>
       </c>
       <c r="B12" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404983</v>
+        <v>404596</v>
       </c>
       <c r="R12" t="n">
-        <v>6795860</v>
+        <v>6796024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476001</v>
+        <v>129476032</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>92888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404789</v>
+        <v>404618</v>
       </c>
       <c r="R13" t="n">
-        <v>6795606</v>
+        <v>6795823</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475994</v>
+        <v>129475978</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>90620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404596</v>
+        <v>404977</v>
       </c>
       <c r="R14" t="n">
-        <v>6796024</v>
+        <v>6795858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475978</v>
+        <v>129475969</v>
       </c>
       <c r="B15" t="n">
-        <v>90620</v>
+        <v>79695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404977</v>
+        <v>404983</v>
       </c>
       <c r="R15" t="n">
-        <v>6795858</v>
+        <v>6795860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129475981</v>
+        <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>78834</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404597</v>
+        <v>404846</v>
       </c>
       <c r="R17" t="n">
-        <v>6795875</v>
+        <v>6795943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476028</v>
+        <v>129476027</v>
       </c>
       <c r="B18" t="n">
         <v>92870</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404846</v>
+        <v>405008</v>
       </c>
       <c r="R18" t="n">
-        <v>6795943</v>
+        <v>6795837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476027</v>
+        <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>92870</v>
+        <v>78834</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405008</v>
+        <v>404597</v>
       </c>
       <c r="R19" t="n">
-        <v>6795837</v>
+        <v>6795875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129475975</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405119</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795655</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79076</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79076</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R24" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129475974</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>405050</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B28" t="n">
         <v>79076</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129475997</v>
       </c>
       <c r="B29" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404617</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B40" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R40" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>92888</v>
+        <v>79695</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R41" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>92888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>92870</v>
+        <v>79695</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R47" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B48" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B49" t="n">
-        <v>78834</v>
+        <v>92870</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>78834</v>
+        <v>92870</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R57" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>92870</v>
+        <v>78834</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R58" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129476021</v>
       </c>
       <c r="B2" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129475991</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129475972</v>
       </c>
       <c r="B4" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129475999</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>129475984</v>
       </c>
       <c r="B9" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129475990</v>
       </c>
       <c r="B10" t="n">
-        <v>81061</v>
+        <v>81066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476001</v>
+        <v>129475994</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404789</v>
+        <v>404596</v>
       </c>
       <c r="R11" t="n">
-        <v>6795606</v>
+        <v>6796024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475994</v>
+        <v>129476001</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404596</v>
+        <v>404789</v>
       </c>
       <c r="R12" t="n">
-        <v>6796024</v>
+        <v>6795606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>129476032</v>
       </c>
       <c r="B13" t="n">
-        <v>92888</v>
+        <v>92893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475978</v>
+        <v>129475989</v>
       </c>
       <c r="B14" t="n">
-        <v>90620</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404977</v>
+        <v>404659</v>
       </c>
       <c r="R14" t="n">
-        <v>6795858</v>
+        <v>6796150</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475969</v>
+        <v>129475978</v>
       </c>
       <c r="B15" t="n">
-        <v>79695</v>
+        <v>90625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404983</v>
+        <v>404977</v>
       </c>
       <c r="R15" t="n">
-        <v>6795860</v>
+        <v>6795858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129475969</v>
       </c>
       <c r="B16" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404983</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6795860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129475968</v>
       </c>
       <c r="B20" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476008</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>405029</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795732</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129476000</v>
       </c>
       <c r="B25" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>404752</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795618</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129475997</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404617</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475974</v>
+        <v>129476007</v>
       </c>
       <c r="B27" t="n">
-        <v>79666</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405050</v>
+        <v>405036</v>
       </c>
       <c r="R27" t="n">
-        <v>6795647</v>
+        <v>6795690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476000</v>
+        <v>129476024</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404752</v>
+        <v>404978</v>
       </c>
       <c r="R28" t="n">
-        <v>6795618</v>
+        <v>6795580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>92870</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,7 +3781,7 @@
         <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>79695</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4102,7 @@
         <v>129475986</v>
       </c>
       <c r="B34" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129475995</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R40" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4958,7 @@
         <v>129476031</v>
       </c>
       <c r="B42" t="n">
-        <v>92888</v>
+        <v>92893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129475982</v>
+        <v>129476005</v>
       </c>
       <c r="B44" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404585</v>
+        <v>404990</v>
       </c>
       <c r="R44" t="n">
-        <v>6795876</v>
+        <v>6795675</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476005</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404990</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795675</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,7 +5493,7 @@
         <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>78834</v>
+        <v>92875</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R48" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>92870</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B51" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129476014</v>
       </c>
       <c r="B52" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>404889</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795906</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
         <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R55" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R56" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B57" t="n">
-        <v>92870</v>
+        <v>78839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R57" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B58" t="n">
-        <v>78834</v>
+        <v>92875</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R58" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
         <v>129475977</v>
       </c>
       <c r="B59" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476020</v>
+        <v>129476006</v>
       </c>
       <c r="B60" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>405094</v>
+        <v>405010</v>
       </c>
       <c r="R60" t="n">
-        <v>6795659</v>
+        <v>6795690</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476017</v>
+        <v>129476009</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404825</v>
+        <v>404999</v>
       </c>
       <c r="R61" t="n">
-        <v>6795955</v>
+        <v>6795773</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476009</v>
+        <v>129476017</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404999</v>
+        <v>404825</v>
       </c>
       <c r="R62" t="n">
-        <v>6795773</v>
+        <v>6795955</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476006</v>
+        <v>129476020</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405010</v>
+        <v>405094</v>
       </c>
       <c r="R63" t="n">
-        <v>6795690</v>
+        <v>6795659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476033</v>
+        <v>129475984</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>78839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404617</v>
+        <v>404976</v>
       </c>
       <c r="R8" t="n">
-        <v>6795935</v>
+        <v>6795654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129475984</v>
+        <v>129476033</v>
       </c>
       <c r="B9" t="n">
-        <v>78839</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404976</v>
+        <v>404617</v>
       </c>
       <c r="R9" t="n">
-        <v>6795654</v>
+        <v>6795935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475990</v>
+        <v>129475978</v>
       </c>
       <c r="B10" t="n">
-        <v>81066</v>
+        <v>90625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404665</v>
+        <v>404977</v>
       </c>
       <c r="R10" t="n">
-        <v>6796141</v>
+        <v>6795858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475994</v>
+        <v>129476001</v>
       </c>
       <c r="B11" t="n">
         <v>79081</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404596</v>
+        <v>404789</v>
       </c>
       <c r="R11" t="n">
-        <v>6796024</v>
+        <v>6795606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476001</v>
+        <v>129475994</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404789</v>
+        <v>404596</v>
       </c>
       <c r="R12" t="n">
-        <v>6795606</v>
+        <v>6796024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129476032</v>
+        <v>129475990</v>
       </c>
       <c r="B13" t="n">
-        <v>92893</v>
+        <v>81066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4368</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404618</v>
+        <v>404665</v>
       </c>
       <c r="R13" t="n">
-        <v>6795823</v>
+        <v>6796141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475989</v>
+        <v>129476032</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>92893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4368</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404659</v>
+        <v>404618</v>
       </c>
       <c r="R14" t="n">
-        <v>6796150</v>
+        <v>6795823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475978</v>
+        <v>129475969</v>
       </c>
       <c r="B15" t="n">
-        <v>90625</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404977</v>
+        <v>404983</v>
       </c>
       <c r="R15" t="n">
-        <v>6795858</v>
+        <v>6795860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475969</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404983</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6795860</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476027</v>
+        <v>129475981</v>
       </c>
       <c r="B18" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405008</v>
+        <v>404597</v>
       </c>
       <c r="R18" t="n">
-        <v>6795837</v>
+        <v>6795875</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B19" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R19" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476010</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404943</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795899</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476008</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405029</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795732</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476000</v>
+        <v>129476007</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404752</v>
+        <v>405036</v>
       </c>
       <c r="R25" t="n">
-        <v>6795618</v>
+        <v>6795690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129475997</v>
+        <v>129476000</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404617</v>
+        <v>404752</v>
       </c>
       <c r="R26" t="n">
-        <v>6795687</v>
+        <v>6795618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476007</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405036</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795690</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476024</v>
+        <v>129475974</v>
       </c>
       <c r="B28" t="n">
-        <v>92875</v>
+        <v>79671</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404978</v>
+        <v>405050</v>
       </c>
       <c r="R28" t="n">
-        <v>6795580</v>
+        <v>6795647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B29" t="n">
-        <v>79671</v>
+        <v>92875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,7 +3671,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B30" t="n">
         <v>79700</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476022</v>
       </c>
       <c r="B36" t="n">
-        <v>79113</v>
+        <v>78747</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404666</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6796033</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129475961</v>
       </c>
       <c r="B37" t="n">
-        <v>78747</v>
+        <v>79113</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>405083</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795691</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129475965</v>
+        <v>129476031</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>92893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4368</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405075</v>
+        <v>404617</v>
       </c>
       <c r="R40" t="n">
-        <v>6795660</v>
+        <v>6795929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B42" t="n">
-        <v>92893</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R42" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R47" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475964</v>
+        <v>129475988</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>405045</v>
+        <v>404648</v>
       </c>
       <c r="R50" t="n">
-        <v>6795657</v>
+        <v>6796068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475970</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404726</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795995</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475970</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404726</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R56" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129475985</v>
+        <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404902</v>
+        <v>404975</v>
       </c>
       <c r="R57" t="n">
-        <v>6795911</v>
+        <v>6795584</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,32 +6667,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129476026</v>
+        <v>129475985</v>
       </c>
       <c r="B58" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404975</v>
+        <v>404902</v>
       </c>
       <c r="R58" t="n">
-        <v>6795584</v>
+        <v>6795911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476006</v>
+        <v>129476020</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>405010</v>
+        <v>405094</v>
       </c>
       <c r="R60" t="n">
-        <v>6795690</v>
+        <v>6795659</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,7 +6988,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476009</v>
+        <v>129476017</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404999</v>
+        <v>404825</v>
       </c>
       <c r="R61" t="n">
-        <v>6795773</v>
+        <v>6795955</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,7 +7095,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476017</v>
+        <v>129476009</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404825</v>
+        <v>404999</v>
       </c>
       <c r="R62" t="n">
-        <v>6795955</v>
+        <v>6795773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476020</v>
+        <v>129476006</v>
       </c>
       <c r="B63" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405094</v>
+        <v>405010</v>
       </c>
       <c r="R63" t="n">
-        <v>6795659</v>
+        <v>6795690</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B2" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R2" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R3" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475972</v>
+        <v>129476021</v>
       </c>
       <c r="B4" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404620</v>
+        <v>405019</v>
       </c>
       <c r="R4" t="n">
-        <v>6795717</v>
+        <v>6795811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475973</v>
+        <v>129475991</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404770</v>
+        <v>404585</v>
       </c>
       <c r="R5" t="n">
-        <v>6795623</v>
+        <v>6795876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R7" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475984</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404976</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795654</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129476033</v>
+        <v>129475984</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>78839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404617</v>
+        <v>404976</v>
       </c>
       <c r="R9" t="n">
-        <v>6795935</v>
+        <v>6795654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475978</v>
+        <v>129476032</v>
       </c>
       <c r="B10" t="n">
-        <v>90625</v>
+        <v>92893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404977</v>
+        <v>404618</v>
       </c>
       <c r="R10" t="n">
-        <v>6795858</v>
+        <v>6795823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476001</v>
+        <v>129475989</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404789</v>
+        <v>404659</v>
       </c>
       <c r="R11" t="n">
-        <v>6795606</v>
+        <v>6796150</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475994</v>
+        <v>129475990</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404596</v>
+        <v>404665</v>
       </c>
       <c r="R12" t="n">
-        <v>6796024</v>
+        <v>6796141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475990</v>
+        <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>81066</v>
+        <v>90625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404665</v>
+        <v>404977</v>
       </c>
       <c r="R13" t="n">
-        <v>6796141</v>
+        <v>6795858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476032</v>
+        <v>129476001</v>
       </c>
       <c r="B14" t="n">
-        <v>92893</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404618</v>
+        <v>404789</v>
       </c>
       <c r="R14" t="n">
-        <v>6795823</v>
+        <v>6795606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475969</v>
+        <v>129475994</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404983</v>
+        <v>404596</v>
       </c>
       <c r="R15" t="n">
-        <v>6795860</v>
+        <v>6796024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129475969</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404983</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6795860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R18" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476027</v>
+        <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405008</v>
+        <v>404597</v>
       </c>
       <c r="R19" t="n">
-        <v>6795837</v>
+        <v>6795875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129475975</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>405119</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129475996</v>
       </c>
       <c r="B24" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404614</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B28" t="n">
-        <v>79671</v>
+        <v>92875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R28" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476024</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>92875</v>
+        <v>79671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404978</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795580</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R30" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,7 +3778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B31" t="n">
         <v>79700</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R31" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475992</v>
+        <v>129475963</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404759</v>
+        <v>404602</v>
       </c>
       <c r="R32" t="n">
-        <v>6795618</v>
+        <v>6796090</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475992</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>404759</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795618</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476022</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>78747</v>
+        <v>79113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404666</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6796033</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129475961</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79113</v>
+        <v>78747</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>405083</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795691</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404643</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6796056</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B49" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R49" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475988</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404648</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6796068</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475970</v>
+        <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404726</v>
+        <v>404648</v>
       </c>
       <c r="R53" t="n">
-        <v>6795995</v>
+        <v>6796068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475972</v>
+        <v>129475991</v>
       </c>
       <c r="B2" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404620</v>
+        <v>404585</v>
       </c>
       <c r="R2" t="n">
-        <v>6795717</v>
+        <v>6795876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475973</v>
+        <v>129476021</v>
       </c>
       <c r="B3" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404770</v>
+        <v>405019</v>
       </c>
       <c r="R3" t="n">
-        <v>6795623</v>
+        <v>6795811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129476021</v>
+        <v>129475972</v>
       </c>
       <c r="B4" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405019</v>
+        <v>404620</v>
       </c>
       <c r="R4" t="n">
-        <v>6795811</v>
+        <v>6795717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475991</v>
+        <v>129475973</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404585</v>
+        <v>404770</v>
       </c>
       <c r="R5" t="n">
-        <v>6795876</v>
+        <v>6795623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476032</v>
+        <v>129475978</v>
       </c>
       <c r="B10" t="n">
-        <v>92893</v>
+        <v>90625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4368</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404618</v>
+        <v>404977</v>
       </c>
       <c r="R10" t="n">
-        <v>6795823</v>
+        <v>6795858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475989</v>
+        <v>129476032</v>
       </c>
       <c r="B11" t="n">
-        <v>78839</v>
+        <v>92893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404659</v>
+        <v>404618</v>
       </c>
       <c r="R11" t="n">
-        <v>6796150</v>
+        <v>6795823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475990</v>
+        <v>129476001</v>
       </c>
       <c r="B12" t="n">
-        <v>81066</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404665</v>
+        <v>404789</v>
       </c>
       <c r="R12" t="n">
-        <v>6796141</v>
+        <v>6795606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475978</v>
+        <v>129475994</v>
       </c>
       <c r="B13" t="n">
-        <v>90625</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404977</v>
+        <v>404596</v>
       </c>
       <c r="R13" t="n">
-        <v>6795858</v>
+        <v>6796024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129476001</v>
+        <v>129475990</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404789</v>
+        <v>404665</v>
       </c>
       <c r="R14" t="n">
-        <v>6795606</v>
+        <v>6796141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475994</v>
+        <v>129475969</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404596</v>
+        <v>404983</v>
       </c>
       <c r="R15" t="n">
-        <v>6796024</v>
+        <v>6795860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475969</v>
+        <v>129475989</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404983</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6795860</v>
+        <v>6796150</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129475975</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405119</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795655</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R24" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476007</v>
+        <v>129475974</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405036</v>
+        <v>405050</v>
       </c>
       <c r="R25" t="n">
-        <v>6795690</v>
+        <v>6795647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476000</v>
+        <v>129476024</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404752</v>
+        <v>404978</v>
       </c>
       <c r="R26" t="n">
-        <v>6795618</v>
+        <v>6795580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476007</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>405036</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476024</v>
+        <v>129476000</v>
       </c>
       <c r="B28" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404978</v>
+        <v>404752</v>
       </c>
       <c r="R28" t="n">
-        <v>6795580</v>
+        <v>6795618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129475997</v>
       </c>
       <c r="B29" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404617</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475966</v>
+        <v>129475992</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>405049</v>
+        <v>404759</v>
       </c>
       <c r="R31" t="n">
-        <v>6795727</v>
+        <v>6795618</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475992</v>
+        <v>129475966</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404759</v>
+        <v>405049</v>
       </c>
       <c r="R33" t="n">
-        <v>6795618</v>
+        <v>6795727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B36" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B37" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R39" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129475965</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>405075</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129475982</v>
+        <v>129476016</v>
       </c>
       <c r="B45" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404585</v>
+        <v>404829</v>
       </c>
       <c r="R45" t="n">
-        <v>6795876</v>
+        <v>6795954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129476016</v>
+        <v>129475982</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404829</v>
+        <v>404585</v>
       </c>
       <c r="R46" t="n">
-        <v>6795954</v>
+        <v>6795876</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475970</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404726</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6795995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129475976</v>
+        <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>405003</v>
+        <v>404835</v>
       </c>
       <c r="R56" t="n">
-        <v>6795853</v>
+        <v>6795953</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129475993</v>
+        <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405005</v>
+        <v>404617</v>
       </c>
       <c r="R7" t="n">
-        <v>6795847</v>
+        <v>6795935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129476033</v>
+        <v>129475993</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R8" t="n">
-        <v>6795935</v>
+        <v>6795847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475978</v>
+        <v>129475969</v>
       </c>
       <c r="B10" t="n">
-        <v>90625</v>
+        <v>79700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404977</v>
+        <v>404983</v>
       </c>
       <c r="R10" t="n">
-        <v>6795858</v>
+        <v>6795860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129476032</v>
+        <v>129475978</v>
       </c>
       <c r="B11" t="n">
-        <v>92893</v>
+        <v>90629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404618</v>
+        <v>404977</v>
       </c>
       <c r="R11" t="n">
-        <v>6795823</v>
+        <v>6795858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476001</v>
+        <v>129476032</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>92897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404789</v>
+        <v>404618</v>
       </c>
       <c r="R12" t="n">
-        <v>6795606</v>
+        <v>6795823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475994</v>
+        <v>129475989</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404596</v>
+        <v>404659</v>
       </c>
       <c r="R13" t="n">
-        <v>6796024</v>
+        <v>6796150</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475969</v>
+        <v>129476001</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404983</v>
+        <v>404789</v>
       </c>
       <c r="R15" t="n">
-        <v>6795860</v>
+        <v>6795606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475989</v>
+        <v>129475994</v>
       </c>
       <c r="B16" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404596</v>
       </c>
       <c r="R16" t="n">
-        <v>6796150</v>
+        <v>6796024</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129476027</v>
       </c>
       <c r="B18" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129475975</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>405119</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129476008</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>405029</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795732</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129476010</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>404943</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129475996</v>
       </c>
       <c r="B24" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404614</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795700</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>79671</v>
+        <v>92879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R25" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B26" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R26" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476007</v>
+        <v>129476000</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405036</v>
+        <v>404752</v>
       </c>
       <c r="R27" t="n">
-        <v>6795690</v>
+        <v>6795618</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129476000</v>
+        <v>129475997</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404752</v>
+        <v>404617</v>
       </c>
       <c r="R28" t="n">
-        <v>6795618</v>
+        <v>6795687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R29" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129476030</v>
+        <v>129475963</v>
       </c>
       <c r="B30" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404647</v>
+        <v>404602</v>
       </c>
       <c r="R30" t="n">
-        <v>6796135</v>
+        <v>6796090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475963</v>
+        <v>129475966</v>
       </c>
       <c r="B32" t="n">
         <v>79700</v>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404602</v>
+        <v>405049</v>
       </c>
       <c r="R32" t="n">
-        <v>6796090</v>
+        <v>6795727</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475966</v>
+        <v>129476030</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405049</v>
+        <v>404647</v>
       </c>
       <c r="R33" t="n">
-        <v>6795727</v>
+        <v>6796135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129476002</v>
+        <v>129475961</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404928</v>
+        <v>405083</v>
       </c>
       <c r="R36" t="n">
-        <v>6795555</v>
+        <v>6795691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476018</v>
+        <v>129476022</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404741</v>
+        <v>404666</v>
       </c>
       <c r="R37" t="n">
-        <v>6795997</v>
+        <v>6796033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129475961</v>
+        <v>129476002</v>
       </c>
       <c r="B38" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405083</v>
+        <v>404928</v>
       </c>
       <c r="R38" t="n">
-        <v>6795691</v>
+        <v>6795555</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476022</v>
+        <v>129476018</v>
       </c>
       <c r="B39" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404666</v>
+        <v>404741</v>
       </c>
       <c r="R39" t="n">
-        <v>6796033</v>
+        <v>6795997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129476031</v>
+        <v>129475965</v>
       </c>
       <c r="B40" t="n">
-        <v>92893</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404617</v>
+        <v>405075</v>
       </c>
       <c r="R40" t="n">
-        <v>6795929</v>
+        <v>6795660</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>92897</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129475965</v>
+        <v>129476019</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405075</v>
+        <v>404638</v>
       </c>
       <c r="R42" t="n">
-        <v>6795660</v>
+        <v>6796042</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475970</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404726</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6795995</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475976</v>
+        <v>129476004</v>
       </c>
       <c r="B54" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>405003</v>
+        <v>404984</v>
       </c>
       <c r="R54" t="n">
-        <v>6795853</v>
+        <v>6795620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476004</v>
+        <v>129476015</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404984</v>
+        <v>404835</v>
       </c>
       <c r="R55" t="n">
-        <v>6795620</v>
+        <v>6795953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476015</v>
+        <v>129475976</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404835</v>
+        <v>405003</v>
       </c>
       <c r="R56" t="n">
-        <v>6795953</v>
+        <v>6795853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129475991</v>
+        <v>129476021</v>
       </c>
       <c r="B2" t="n">
-        <v>78838</v>
+        <v>78747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404585</v>
+        <v>405019</v>
       </c>
       <c r="R2" t="n">
-        <v>6795876</v>
+        <v>6795811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129476021</v>
+        <v>129475991</v>
       </c>
       <c r="B3" t="n">
-        <v>78747</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405019</v>
+        <v>404585</v>
       </c>
       <c r="R3" t="n">
-        <v>6795811</v>
+        <v>6795876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1213,7 +1213,7 @@
         <v>129476033</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475993</v>
+        <v>129475984</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405005</v>
+        <v>404976</v>
       </c>
       <c r="R8" t="n">
-        <v>6795847</v>
+        <v>6795654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129475984</v>
+        <v>129475993</v>
       </c>
       <c r="B9" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404976</v>
+        <v>405005</v>
       </c>
       <c r="R9" t="n">
-        <v>6795654</v>
+        <v>6795847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129475969</v>
+        <v>129476001</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404983</v>
+        <v>404789</v>
       </c>
       <c r="R10" t="n">
-        <v>6795860</v>
+        <v>6795606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475978</v>
+        <v>129475994</v>
       </c>
       <c r="B11" t="n">
-        <v>90629</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404977</v>
+        <v>404596</v>
       </c>
       <c r="R11" t="n">
-        <v>6795858</v>
+        <v>6796024</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129476032</v>
+        <v>129475969</v>
       </c>
       <c r="B12" t="n">
-        <v>92897</v>
+        <v>79700</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404618</v>
+        <v>404983</v>
       </c>
       <c r="R12" t="n">
-        <v>6795823</v>
+        <v>6795860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475989</v>
+        <v>129475978</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>90631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404659</v>
+        <v>404977</v>
       </c>
       <c r="R13" t="n">
-        <v>6796150</v>
+        <v>6795858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475990</v>
+        <v>129475989</v>
       </c>
       <c r="B14" t="n">
-        <v>81066</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404665</v>
+        <v>404659</v>
       </c>
       <c r="R14" t="n">
-        <v>6796141</v>
+        <v>6796150</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129476001</v>
+        <v>129475990</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>81066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404789</v>
+        <v>404665</v>
       </c>
       <c r="R15" t="n">
-        <v>6795606</v>
+        <v>6796141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129475994</v>
+        <v>129476032</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>92899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404596</v>
+        <v>404618</v>
       </c>
       <c r="R16" t="n">
-        <v>6796024</v>
+        <v>6795823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476028</v>
+        <v>129475981</v>
       </c>
       <c r="B17" t="n">
-        <v>92879</v>
+        <v>78839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404846</v>
+        <v>404597</v>
       </c>
       <c r="R17" t="n">
-        <v>6795943</v>
+        <v>6795875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476027</v>
+        <v>129476028</v>
       </c>
       <c r="B18" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405008</v>
+        <v>404846</v>
       </c>
       <c r="R18" t="n">
-        <v>6795837</v>
+        <v>6795943</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129475981</v>
+        <v>129476027</v>
       </c>
       <c r="B19" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404597</v>
+        <v>405008</v>
       </c>
       <c r="R19" t="n">
-        <v>6795875</v>
+        <v>6795837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3139,7 +3139,7 @@
         <v>129476024</v>
       </c>
       <c r="B25" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129476030</v>
+        <v>129475986</v>
       </c>
       <c r="B33" t="n">
-        <v>92879</v>
+        <v>78839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404647</v>
+        <v>404709</v>
       </c>
       <c r="R33" t="n">
-        <v>6796135</v>
+        <v>6795944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129475986</v>
+        <v>129476030</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404709</v>
+        <v>404647</v>
       </c>
       <c r="R34" t="n">
-        <v>6795944</v>
+        <v>6796135</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476031</v>
+        <v>129476019</v>
       </c>
       <c r="B41" t="n">
-        <v>92897</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404617</v>
+        <v>404638</v>
       </c>
       <c r="R41" t="n">
-        <v>6795929</v>
+        <v>6796042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476019</v>
+        <v>129476031</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>92899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4368</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404638</v>
+        <v>404617</v>
       </c>
       <c r="R42" t="n">
-        <v>6796042</v>
+        <v>6795929</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
         <v>129476023</v>
       </c>
       <c r="B43" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475971</v>
+        <v>129475983</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404652</v>
+        <v>404762</v>
       </c>
       <c r="R47" t="n">
-        <v>6796177</v>
+        <v>6795619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475971</v>
       </c>
       <c r="B48" t="n">
-        <v>92879</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404652</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6796177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129476029</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404643</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6796056</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475988</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404648</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6796068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129476014</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404889</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475964</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>405045</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475970</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404726</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6563,7 +6563,7 @@
         <v>129476026</v>
       </c>
       <c r="B57" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129475981</v>
+        <v>129476028</v>
       </c>
       <c r="B17" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404597</v>
+        <v>404846</v>
       </c>
       <c r="R17" t="n">
-        <v>6795875</v>
+        <v>6795943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476028</v>
+        <v>129476027</v>
       </c>
       <c r="B18" t="n">
         <v>92881</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404846</v>
+        <v>405008</v>
       </c>
       <c r="R18" t="n">
-        <v>6795943</v>
+        <v>6795837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129476027</v>
+        <v>129475981</v>
       </c>
       <c r="B19" t="n">
-        <v>92881</v>
+        <v>78839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405008</v>
+        <v>404597</v>
       </c>
       <c r="R19" t="n">
-        <v>6795837</v>
+        <v>6795875</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129475975</v>
+        <v>129476008</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405119</v>
+        <v>405029</v>
       </c>
       <c r="R21" t="n">
-        <v>6795655</v>
+        <v>6795732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476008</v>
+        <v>129476010</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405029</v>
+        <v>404943</v>
       </c>
       <c r="R22" t="n">
-        <v>6795732</v>
+        <v>6795899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129476010</v>
+        <v>129475996</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404943</v>
+        <v>404614</v>
       </c>
       <c r="R23" t="n">
-        <v>6795899</v>
+        <v>6795700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475996</v>
+        <v>129475975</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404614</v>
+        <v>405119</v>
       </c>
       <c r="R24" t="n">
-        <v>6795700</v>
+        <v>6795655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129475988</v>
+        <v>129476014</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404648</v>
+        <v>404889</v>
       </c>
       <c r="R50" t="n">
-        <v>6796068</v>
+        <v>6795906</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129476014</v>
+        <v>129475964</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404889</v>
+        <v>405045</v>
       </c>
       <c r="R51" t="n">
-        <v>6795906</v>
+        <v>6795657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475964</v>
+        <v>129475970</v>
       </c>
       <c r="B52" t="n">
         <v>79700</v>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405045</v>
+        <v>404726</v>
       </c>
       <c r="R52" t="n">
-        <v>6795657</v>
+        <v>6795995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475970</v>
+        <v>129475988</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404726</v>
+        <v>404648</v>
       </c>
       <c r="R53" t="n">
-        <v>6795995</v>
+        <v>6796068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476024</v>
+        <v>129476007</v>
       </c>
       <c r="B25" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404978</v>
+        <v>405036</v>
       </c>
       <c r="R25" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476007</v>
+        <v>129476000</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405036</v>
+        <v>404752</v>
       </c>
       <c r="R26" t="n">
-        <v>6795690</v>
+        <v>6795618</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129476000</v>
+        <v>129475997</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404752</v>
+        <v>404617</v>
       </c>
       <c r="R27" t="n">
-        <v>6795618</v>
+        <v>6795687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475997</v>
+        <v>129475974</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404617</v>
+        <v>405050</v>
       </c>
       <c r="R28" t="n">
-        <v>6795687</v>
+        <v>6795647</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129475974</v>
+        <v>129476024</v>
       </c>
       <c r="B29" t="n">
-        <v>79671</v>
+        <v>92881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405050</v>
+        <v>404978</v>
       </c>
       <c r="R29" t="n">
-        <v>6795647</v>
+        <v>6795580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475983</v>
+        <v>129475971</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404762</v>
+        <v>404652</v>
       </c>
       <c r="R47" t="n">
-        <v>6795619</v>
+        <v>6796177</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129475971</v>
+        <v>129476029</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404652</v>
+        <v>404643</v>
       </c>
       <c r="R48" t="n">
-        <v>6796177</v>
+        <v>6796056</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5704,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129476029</v>
+        <v>129475983</v>
       </c>
       <c r="B49" t="n">
-        <v>92881</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404643</v>
+        <v>404762</v>
       </c>
       <c r="R49" t="n">
-        <v>6796056</v>
+        <v>6795619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129476004</v>
+        <v>129475976</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404984</v>
+        <v>405003</v>
       </c>
       <c r="R54" t="n">
-        <v>6795620</v>
+        <v>6795853</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6346,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476015</v>
+        <v>129476004</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404835</v>
+        <v>404984</v>
       </c>
       <c r="R55" t="n">
-        <v>6795953</v>
+        <v>6795620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129475976</v>
+        <v>129476015</v>
       </c>
       <c r="B56" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>405003</v>
+        <v>404835</v>
       </c>
       <c r="R56" t="n">
-        <v>6795853</v>
+        <v>6795953</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129476021</v>
+        <v>129475961</v>
       </c>
       <c r="B2" t="n">
-        <v>78747</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405019</v>
+        <v>405083</v>
       </c>
       <c r="R2" t="n">
-        <v>6795811</v>
+        <v>6795691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129475991</v>
+        <v>129476020</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404585</v>
+        <v>405094</v>
       </c>
       <c r="R3" t="n">
-        <v>6795876</v>
+        <v>6795659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129475972</v>
+        <v>129476021</v>
       </c>
       <c r="B4" t="n">
-        <v>79671</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404620</v>
+        <v>405019</v>
       </c>
       <c r="R4" t="n">
-        <v>6795717</v>
+        <v>6795811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129475973</v>
+        <v>129476022</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404770</v>
+        <v>404666</v>
       </c>
       <c r="R5" t="n">
-        <v>6795623</v>
+        <v>6796033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129475999</v>
+        <v>129475990</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404725</v>
+        <v>404665</v>
       </c>
       <c r="R6" t="n">
-        <v>6795585</v>
+        <v>6796141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129476033</v>
+        <v>129475978</v>
       </c>
       <c r="B7" t="n">
-        <v>92875</v>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404617</v>
+        <v>404977</v>
       </c>
       <c r="R7" t="n">
-        <v>6795935</v>
+        <v>6795858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129475984</v>
+        <v>129476033</v>
       </c>
       <c r="B8" t="n">
-        <v>78839</v>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404976</v>
+        <v>404617</v>
       </c>
       <c r="R8" t="n">
-        <v>6795654</v>
+        <v>6795935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129475993</v>
+        <v>129476023</v>
       </c>
       <c r="B9" t="n">
-        <v>78838</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405005</v>
+        <v>404612</v>
       </c>
       <c r="R9" t="n">
-        <v>6795847</v>
+        <v>6795706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129476001</v>
+        <v>129476024</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404789</v>
+        <v>404978</v>
       </c>
       <c r="R10" t="n">
-        <v>6795606</v>
+        <v>6795580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129475994</v>
+        <v>129476026</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404596</v>
+        <v>404975</v>
       </c>
       <c r="R11" t="n">
-        <v>6796024</v>
+        <v>6795584</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129475969</v>
+        <v>129476027</v>
       </c>
       <c r="B12" t="n">
-        <v>79700</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404983</v>
+        <v>405008</v>
       </c>
       <c r="R12" t="n">
-        <v>6795860</v>
+        <v>6795837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129475978</v>
+        <v>129476028</v>
       </c>
       <c r="B13" t="n">
-        <v>90631</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404977</v>
+        <v>404846</v>
       </c>
       <c r="R13" t="n">
-        <v>6795858</v>
+        <v>6795943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129475989</v>
+        <v>129476029</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404659</v>
+        <v>404643</v>
       </c>
       <c r="R14" t="n">
-        <v>6796150</v>
+        <v>6796056</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129475990</v>
+        <v>129476030</v>
       </c>
       <c r="B15" t="n">
-        <v>81066</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404665</v>
+        <v>404647</v>
       </c>
       <c r="R15" t="n">
-        <v>6796141</v>
+        <v>6796135</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129476032</v>
+        <v>129476031</v>
       </c>
       <c r="B16" t="n">
-        <v>92899</v>
+        <v>93215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404618</v>
+        <v>404617</v>
       </c>
       <c r="R16" t="n">
-        <v>6795823</v>
+        <v>6795929</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129476028</v>
+        <v>129476032</v>
       </c>
       <c r="B17" t="n">
-        <v>92881</v>
+        <v>93215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4368</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404846</v>
+        <v>404618</v>
       </c>
       <c r="R17" t="n">
-        <v>6795943</v>
+        <v>6795823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129476027</v>
+        <v>129475994</v>
       </c>
       <c r="B18" t="n">
-        <v>92881</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405008</v>
+        <v>404596</v>
       </c>
       <c r="R18" t="n">
-        <v>6795837</v>
+        <v>6796024</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129475981</v>
+        <v>129475995</v>
       </c>
       <c r="B19" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404597</v>
+        <v>404608</v>
       </c>
       <c r="R19" t="n">
-        <v>6795875</v>
+        <v>6795715</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129475968</v>
+        <v>129475996</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405003</v>
+        <v>404614</v>
       </c>
       <c r="R20" t="n">
-        <v>6795853</v>
+        <v>6795700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129476008</v>
+        <v>129475997</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405029</v>
+        <v>404617</v>
       </c>
       <c r="R21" t="n">
-        <v>6795732</v>
+        <v>6795687</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,14 +2815,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129476010</v>
+        <v>129475998</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404943</v>
+        <v>404654</v>
       </c>
       <c r="R22" t="n">
-        <v>6795899</v>
+        <v>6795634</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,14 +2922,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129475996</v>
+        <v>129475999</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404614</v>
+        <v>404725</v>
       </c>
       <c r="R23" t="n">
-        <v>6795700</v>
+        <v>6795585</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,32 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129475975</v>
+        <v>129476000</v>
       </c>
       <c r="B24" t="n">
-        <v>79671</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405119</v>
+        <v>404752</v>
       </c>
       <c r="R24" t="n">
-        <v>6795655</v>
+        <v>6795618</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,14 +3136,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129476007</v>
+        <v>129476001</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405036</v>
+        <v>404789</v>
       </c>
       <c r="R25" t="n">
-        <v>6795690</v>
+        <v>6795606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,14 +3243,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129476000</v>
+        <v>129476002</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404752</v>
+        <v>404928</v>
       </c>
       <c r="R26" t="n">
-        <v>6795618</v>
+        <v>6795555</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,14 +3350,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129475997</v>
+        <v>129476004</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404617</v>
+        <v>404984</v>
       </c>
       <c r="R27" t="n">
-        <v>6795687</v>
+        <v>6795620</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129475974</v>
+        <v>129476005</v>
       </c>
       <c r="B28" t="n">
-        <v>79671</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405050</v>
+        <v>404990</v>
       </c>
       <c r="R28" t="n">
-        <v>6795647</v>
+        <v>6795675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129476024</v>
+        <v>129476006</v>
       </c>
       <c r="B29" t="n">
-        <v>92881</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404978</v>
+        <v>405010</v>
       </c>
       <c r="R29" t="n">
-        <v>6795580</v>
+        <v>6795690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129475963</v>
+        <v>129476007</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404602</v>
+        <v>405036</v>
       </c>
       <c r="R30" t="n">
-        <v>6796090</v>
+        <v>6795690</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129475992</v>
+        <v>129476008</v>
       </c>
       <c r="B31" t="n">
-        <v>78838</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404759</v>
+        <v>405029</v>
       </c>
       <c r="R31" t="n">
-        <v>6795618</v>
+        <v>6795732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,32 +3885,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129475966</v>
+        <v>129476009</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405049</v>
+        <v>404999</v>
       </c>
       <c r="R32" t="n">
-        <v>6795727</v>
+        <v>6795773</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,32 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129475986</v>
+        <v>129476010</v>
       </c>
       <c r="B33" t="n">
-        <v>78839</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404709</v>
+        <v>404943</v>
       </c>
       <c r="R33" t="n">
-        <v>6795944</v>
+        <v>6795899</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,32 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129476030</v>
+        <v>129476014</v>
       </c>
       <c r="B34" t="n">
-        <v>92881</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404647</v>
+        <v>404889</v>
       </c>
       <c r="R34" t="n">
-        <v>6796135</v>
+        <v>6795906</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,14 +4206,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129475995</v>
+        <v>129476015</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>404608</v>
+        <v>404835</v>
       </c>
       <c r="R35" t="n">
-        <v>6795715</v>
+        <v>6795953</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,32 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129475961</v>
+        <v>129476016</v>
       </c>
       <c r="B36" t="n">
-        <v>79113</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405083</v>
+        <v>404829</v>
       </c>
       <c r="R36" t="n">
-        <v>6795691</v>
+        <v>6795954</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,32 +4420,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129476022</v>
+        <v>129476017</v>
       </c>
       <c r="B37" t="n">
-        <v>78747</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404666</v>
+        <v>404825</v>
       </c>
       <c r="R37" t="n">
-        <v>6796033</v>
+        <v>6795955</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,14 +4527,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129476002</v>
+        <v>129476018</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404928</v>
+        <v>404741</v>
       </c>
       <c r="R38" t="n">
-        <v>6795555</v>
+        <v>6795997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,14 +4634,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129476018</v>
+        <v>129476019</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404741</v>
+        <v>404638</v>
       </c>
       <c r="R39" t="n">
-        <v>6795997</v>
+        <v>6796042</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129475965</v>
+        <v>129475991</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405075</v>
+        <v>404585</v>
       </c>
       <c r="R40" t="n">
-        <v>6795660</v>
+        <v>6795876</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129476019</v>
+        <v>129475992</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404638</v>
+        <v>404759</v>
       </c>
       <c r="R41" t="n">
-        <v>6796042</v>
+        <v>6795618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129476031</v>
+        <v>129475993</v>
       </c>
       <c r="B42" t="n">
-        <v>92899</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404617</v>
+        <v>405005</v>
       </c>
       <c r="R42" t="n">
-        <v>6795929</v>
+        <v>6795847</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,32 +5062,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129476023</v>
+        <v>129475963</v>
       </c>
       <c r="B43" t="n">
-        <v>92881</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404612</v>
+        <v>404602</v>
       </c>
       <c r="R43" t="n">
-        <v>6795706</v>
+        <v>6796090</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129476005</v>
+        <v>129475964</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404990</v>
+        <v>405045</v>
       </c>
       <c r="R44" t="n">
-        <v>6795675</v>
+        <v>6795657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129476016</v>
+        <v>129475965</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404829</v>
+        <v>405075</v>
       </c>
       <c r="R45" t="n">
-        <v>6795954</v>
+        <v>6795660</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129475982</v>
+        <v>129475966</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404585</v>
+        <v>405049</v>
       </c>
       <c r="R46" t="n">
-        <v>6795876</v>
+        <v>6795727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129475971</v>
+        <v>129475968</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404652</v>
+        <v>405003</v>
       </c>
       <c r="R47" t="n">
-        <v>6796177</v>
+        <v>6795853</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129476029</v>
+        <v>129475969</v>
       </c>
       <c r="B48" t="n">
-        <v>92881</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404643</v>
+        <v>404983</v>
       </c>
       <c r="R48" t="n">
-        <v>6796056</v>
+        <v>6795860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129475983</v>
+        <v>129475970</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404762</v>
+        <v>404726</v>
       </c>
       <c r="R49" t="n">
-        <v>6795619</v>
+        <v>6795995</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129476014</v>
+        <v>129475971</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404889</v>
+        <v>404652</v>
       </c>
       <c r="R50" t="n">
-        <v>6795906</v>
+        <v>6796177</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129475964</v>
+        <v>129475981</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405045</v>
+        <v>404597</v>
       </c>
       <c r="R51" t="n">
-        <v>6795657</v>
+        <v>6795875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129475970</v>
+        <v>129475982</v>
       </c>
       <c r="B52" t="n">
-        <v>79700</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404726</v>
+        <v>404585</v>
       </c>
       <c r="R52" t="n">
-        <v>6795995</v>
+        <v>6795876</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129475988</v>
+        <v>129475983</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404648</v>
+        <v>404762</v>
       </c>
       <c r="R53" t="n">
-        <v>6796068</v>
+        <v>6795619</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129475976</v>
+        <v>129475984</v>
       </c>
       <c r="B54" t="n">
-        <v>79671</v>
+        <v>79085</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>405003</v>
+        <v>404976</v>
       </c>
       <c r="R54" t="n">
-        <v>6795853</v>
+        <v>6795654</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129476004</v>
+        <v>129475985</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404984</v>
+        <v>404902</v>
       </c>
       <c r="R55" t="n">
-        <v>6795620</v>
+        <v>6795911</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129476015</v>
+        <v>129475986</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404835</v>
+        <v>404709</v>
       </c>
       <c r="R56" t="n">
-        <v>6795953</v>
+        <v>6795944</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,32 +6560,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129476026</v>
+        <v>129475988</v>
       </c>
       <c r="B57" t="n">
-        <v>92881</v>
+        <v>79085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404975</v>
+        <v>404648</v>
       </c>
       <c r="R57" t="n">
-        <v>6795584</v>
+        <v>6796068</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129475985</v>
+        <v>129475989</v>
       </c>
       <c r="B58" t="n">
-        <v>78839</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404902</v>
+        <v>404659</v>
       </c>
       <c r="R58" t="n">
-        <v>6795911</v>
+        <v>6796150</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6774,10 +6774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129475977</v>
+        <v>129475972</v>
       </c>
       <c r="B59" t="n">
-        <v>79671</v>
+        <v>79917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404709</v>
+        <v>404620</v>
       </c>
       <c r="R59" t="n">
-        <v>6795945</v>
+        <v>6795717</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129476020</v>
+        <v>129475973</v>
       </c>
       <c r="B60" t="n">
-        <v>78747</v>
+        <v>79917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>405094</v>
+        <v>404770</v>
       </c>
       <c r="R60" t="n">
-        <v>6795659</v>
+        <v>6795623</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,10 +6988,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129476017</v>
+        <v>129475974</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>79917</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404825</v>
+        <v>405050</v>
       </c>
       <c r="R61" t="n">
-        <v>6795955</v>
+        <v>6795647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129476009</v>
+        <v>129475975</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79917</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,21 +7106,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404999</v>
+        <v>405119</v>
       </c>
       <c r="R62" t="n">
-        <v>6795773</v>
+        <v>6795655</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129476006</v>
+        <v>129475976</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79917</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405010</v>
+        <v>405003</v>
       </c>
       <c r="R63" t="n">
-        <v>6795690</v>
+        <v>6795853</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7306,6 +7306,113 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129475977</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Väster om Nysäterkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>404709</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6795945</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44563-2025 artfynd.xlsx
+++ b/artfynd/A 44563-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476033</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476023</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476027</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476028</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476029</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476030</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476031</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476032</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475994</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475995</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475996</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475997</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475998</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475999</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476000</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476002</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476004</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476005</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476006</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476007</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476008</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476009</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476010</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476014</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476015</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476016</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476017</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476018</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476019</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475991</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475992</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475993</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475963</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475964</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475965</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475966</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475968</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475969</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475970</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475971</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475981</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475982</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475983</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475984</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475985</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475986</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475988</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475989</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475972</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475973</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475974</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475975</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475976</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,8 +7728,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129475977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>